--- a/teacher_forms/015_exam_date_poll_colorful--teacher_forms.xlsx
+++ b/teacher_forms/015_exam_date_poll_colorful--teacher_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,9 +441,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,15 +520,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_1</t>
+          <t>exam_date_form_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>select_exam_date</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Select Exam Date</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>What date would you like to have the exam on?</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>no</t>
@@ -543,15 +547,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_2</t>
+          <t>exam_color_form_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>select_poll_color</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Select Poll Color</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>What color would you like to have for the poll?</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>no</t>
@@ -566,15 +574,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_3</t>
+          <t>exam_period_form_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>select_exam_period</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Select Exam Period</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>What time of day would you like to have the exam on?</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>no</t>
@@ -589,15 +601,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_4</t>
+          <t>exam_date_form_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>exam_date</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Exam Date</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>What date would you like to have the exam on?</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>no</t>
@@ -612,15 +628,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_5</t>
+          <t>exam_time_form_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>exam_time</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Exam Time</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>What time would you like to have the exam on?</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -635,12 +655,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_6</t>
+          <t>exam_date_form_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>select_exam_date</t>
+          <t>Select Exam Date (Repeat)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +678,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_7</t>
+          <t>exam_period_form_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>select_exam_period</t>
+          <t>Select Exam Period (Repeat)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +701,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_8</t>
+          <t>exam_time_form_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>select_exam_time</t>
+          <t>Select Exam Time</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +724,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_9</t>
+          <t>exam_date_form_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>select_exam_date</t>
+          <t>Exam Date Form 9</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +747,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_10</t>
+          <t>exam_form_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>select_exam_period</t>
+          <t>Exam Form 10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -753,10 +773,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="41" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -781,58 +801,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_1_choices</t>
+          <t>exam_date_form_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_1_choices</t>
+          <t>exam_date_form_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_1_choices</t>
+          <t>exam_date_form_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_2_choices</t>
+          <t>exam_color_form_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -849,7 +869,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_2_choices</t>
+          <t>exam_color_form_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -866,7 +886,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_2_choices</t>
+          <t>exam_color_form_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -883,255 +903,306 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_3_choices</t>
+          <t>exam_period_form_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8-00</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8-00</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_3_choices</t>
+          <t>exam_period_form_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>8-30</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8-30</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_3_choices</t>
+          <t>exam_period_form_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>9-00</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9-00</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_6_choices</t>
+          <t>exam_date_form_6_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_6_choices</t>
+          <t>exam_date_form_6_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_7_choices</t>
+          <t>exam_date_form_6_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8-00</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8-00</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_7_choices</t>
+          <t>exam_period_form_7_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>8-30</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8-30</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_7_choices</t>
+          <t>exam_period_form_7_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>9-00</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>9-00</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_8_choices</t>
+          <t>exam_period_form_7_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_8_choices</t>
+          <t>exam_time_form_8_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_9_choices</t>
+          <t>exam_time_form_8_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_9_choices</t>
+          <t>exam_time_form_8_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_10_choices</t>
+          <t>exam_date_form_9_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8-00</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8-00</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_10_choices</t>
+          <t>exam_date_form_9_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>8-30</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8-30</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>exam_date_poll_colorful_form_10_choices</t>
+          <t>exam_date_form_9_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>9-00</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>9-00</t>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>exam_form_10_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>exam_form_10_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>exam_form_10_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
